--- a/news_push_data/all_news/cna/20260403 中央社新聞.xlsx
+++ b/news_push_data/all_news/cna/20260403 中央社新聞.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,276 +2036,6 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>印尼外海強震 北蘇拉威西省建物倒塌已釀1死1傷</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026/04/02 09:44</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-04-02T09:44:00+08:00</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020037.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>川普：未來2到3週將給伊朗最重擊 未達成協議將打擊供電網[影]</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026/04/02 09:29</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-04-02T09:29:00+08:00</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604023002.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>川普全國演說：對伊朗戰爭取得壓倒性勝利[影]</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026/04/02 09:17</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-04-02T09:17:00+08:00</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604023001.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>庫克群島與紐西蘭新簽防務協議 緩解緊張關係</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026/04/02 08:38</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-04-02T08:38:00+08:00</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020023.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>美伊衝突加劇 巴西推動柴油自給計畫</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026/04/02 08:24</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-04-02T08:24:00+08:00</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020022.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>川普將發表全國演說 擬宣布對伊戰爭目標達成[影]</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026/04/02 07:53</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-04-02T07:53:00+08:00</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020019.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>愚人節藝術建國 立陶宛「對岸共和國」歡慶28週年</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026/04/02 07:53</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-04-02T07:53:00+08:00</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020018.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>美出生公民權最高法院開庭 「黃金德案」後代旁聽</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026/04/02 07:45</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-04-02T07:45:00+08:00</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020017.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>印尼東部外海規模7.4強震 引發海嘯警報</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026/04/02 07:41</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026-04-02T07:41:00+08:00</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020016.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>捷克計劃2030年發射首顆國產衛星 強化太空自主性</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2026/04/02 07:24</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-04-02T07:24:00+08:00</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604020015.aspx</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
